--- a/results/542_z18/2_canaliculi/542_z18_canaliculi_results.xlsx
+++ b/results/542_z18/2_canaliculi/542_z18_canaliculi_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,441 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>349.6878</v>
+      </c>
+      <c r="D12" t="n">
+        <v>337.7056</v>
+      </c>
+      <c r="E12" t="n">
+        <v>124.8588</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12006.1818</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12118</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2958.1139</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>28554.2727</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29514</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6304.6903</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.02900112</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.02856139</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.00576019</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03326266</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.03409786</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0063714</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.3636</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.2772</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>per 100 px</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>239.9091</v>
+      </c>
+      <c r="D20" t="n">
+        <v>231</v>
+      </c>
+      <c r="E20" t="n">
+        <v>115.7544</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>479.8182</v>
+      </c>
+      <c r="D21" t="n">
+        <v>438</v>
+      </c>
+      <c r="E21" t="n">
+        <v>237.4463</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>397.1731</v>
+      </c>
+      <c r="D22" t="n">
+        <v>421.5635</v>
+      </c>
+      <c r="E22" t="n">
+        <v>144.9593</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1090.3199</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1145.6438</v>
+      </c>
+      <c r="E23" t="n">
+        <v>345.1069</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9.3636</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.6534</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>13.2727</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.7559</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14.8182</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.115</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>11</v>
       </c>
     </row>
@@ -696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +1353,63 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_length_density_w_per_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.03838905</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_density_without_flagged_per_px</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03399229</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_density_in_roi_per_px</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
         </is>
       </c>
     </row>
@@ -932,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1468,81 @@
           <t>mean_edge_length_px</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1002,6 +1569,51 @@
       <c r="H2" t="n">
         <v>22.5649</v>
       </c>
+      <c r="I2" t="n">
+        <v>142.8112</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4575</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11641</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.04284153</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04544283</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.8009</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>188</v>
+      </c>
+      <c r="R2" t="n">
+        <v>296</v>
+      </c>
+      <c r="S2" t="n">
+        <v>223.5807</v>
+      </c>
+      <c r="T2" t="n">
+        <v>596.1442</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1028,6 +1640,51 @@
       <c r="H3" t="n">
         <v>26.8783</v>
       </c>
+      <c r="I3" t="n">
+        <v>625.725</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16860</v>
+      </c>
+      <c r="K3" t="n">
+        <v>35430</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8861</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.03404508</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03731301</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.0365</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>523</v>
+      </c>
+      <c r="R3" t="n">
+        <v>936</v>
+      </c>
+      <c r="S3" t="n">
+        <v>647.8843000000001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1481.8519</v>
+      </c>
+      <c r="U3" t="n">
+        <v>21</v>
+      </c>
+      <c r="V3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1711,51 @@
       <c r="H4" t="n">
         <v>32.5262</v>
       </c>
+      <c r="I4" t="n">
+        <v>377.0193</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13152</v>
+      </c>
+      <c r="K4" t="n">
+        <v>31926</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02927311</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03270062</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1219</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>231</v>
+      </c>
+      <c r="R4" t="n">
+        <v>570</v>
+      </c>
+      <c r="S4" t="n">
+        <v>421.5635</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1170.7321</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>13</v>
+      </c>
+      <c r="W4" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1782,51 @@
       <c r="H5" t="n">
         <v>41.8034</v>
       </c>
+      <c r="I5" t="n">
+        <v>337.7056</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12118</v>
+      </c>
+      <c r="K5" t="n">
+        <v>29514</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03556693</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03859185</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.0728</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>222</v>
+      </c>
+      <c r="R5" t="n">
+        <v>378</v>
+      </c>
+      <c r="S5" t="n">
+        <v>481.0904</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1305.6266</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>15</v>
+      </c>
+      <c r="W5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1106,6 +1853,51 @@
       <c r="H6" t="n">
         <v>24.1959</v>
       </c>
+      <c r="I6" t="n">
+        <v>371.8061</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13199</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31872</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02492613</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02899096</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.6137</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>170</v>
+      </c>
+      <c r="R6" t="n">
+        <v>228</v>
+      </c>
+      <c r="S6" t="n">
+        <v>367.5341</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1041.2052</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11</v>
+      </c>
+      <c r="W6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1132,6 +1924,51 @@
       <c r="H7" t="n">
         <v>31.5344</v>
       </c>
+      <c r="I7" t="n">
+        <v>308.5929</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11379</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28385</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02856139</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03547648</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.2405</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>254</v>
+      </c>
+      <c r="R7" t="n">
+        <v>630</v>
+      </c>
+      <c r="S7" t="n">
+        <v>361.0488</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1145.6438</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" t="n">
+        <v>15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1158,6 +1995,51 @@
       <c r="H8" t="n">
         <v>25.1068</v>
       </c>
+      <c r="I8" t="n">
+        <v>382.8772</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12760</v>
+      </c>
+      <c r="K8" t="n">
+        <v>30245</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03706897</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.04341213</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.0894</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>302</v>
+      </c>
+      <c r="R8" t="n">
+        <v>649</v>
+      </c>
+      <c r="S8" t="n">
+        <v>537.73</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1477.3961</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1184,6 +2066,51 @@
       <c r="H9" t="n">
         <v>32.3682</v>
       </c>
+      <c r="I9" t="n">
+        <v>306.4924</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10697</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26160</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02823221</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03409786</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2839</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>192</v>
+      </c>
+      <c r="R9" t="n">
+        <v>438</v>
+      </c>
+      <c r="S9" t="n">
+        <v>319.4092</v>
+      </c>
+      <c r="T9" t="n">
+        <v>987.4529</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1210,6 +2137,51 @@
       <c r="H10" t="n">
         <v>26.9002</v>
       </c>
+      <c r="I10" t="n">
+        <v>437.262</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14880</v>
+      </c>
+      <c r="K10" t="n">
+        <v>35351</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.02526882</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.02766541</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.0583</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>235</v>
+      </c>
+      <c r="R10" t="n">
+        <v>393</v>
+      </c>
+      <c r="S10" t="n">
+        <v>422.8183</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1119.5017</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1236,6 +2208,51 @@
       <c r="H11" t="n">
         <v>32.8491</v>
       </c>
+      <c r="I11" t="n">
+        <v>326.8356</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11837</v>
+      </c>
+      <c r="K11" t="n">
+        <v>29271</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.03421475</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.03901472</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4477</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>300</v>
+      </c>
+      <c r="R11" t="n">
+        <v>682</v>
+      </c>
+      <c r="S11" t="n">
+        <v>453.6762</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1281.0874</v>
+      </c>
+      <c r="U11" t="n">
+        <v>12</v>
+      </c>
+      <c r="V11" t="n">
+        <v>16</v>
+      </c>
+      <c r="W11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1262,6 +2279,51 @@
       <c r="H12" t="n">
         <v>35.6555</v>
       </c>
+      <c r="I12" t="n">
+        <v>263.4802</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9968</v>
+      </c>
+      <c r="K12" t="n">
+        <v>22850</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02307384</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.02647702</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2772</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>138</v>
+      </c>
+      <c r="R12" t="n">
+        <v>209</v>
+      </c>
+      <c r="S12" t="n">
+        <v>254.865</v>
+      </c>
+      <c r="T12" t="n">
+        <v>671.2275</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1287,6 +2349,51 @@
       </c>
       <c r="H13" t="n">
         <v>28.9279</v>
+      </c>
+      <c r="I13" t="n">
+        <v>108.7696</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5218</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13093</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.01878114</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02214924</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.7581</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>72</v>
+      </c>
+      <c r="R13" t="n">
+        <v>165</v>
+      </c>
+      <c r="S13" t="n">
+        <v>101.2843</v>
+      </c>
+      <c r="T13" t="n">
+        <v>311.7939</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
